--- a/Luban/Config/Datas/Global.xlsx
+++ b/Luban/Config/Datas/Global.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,26 @@
           <t>artFaceLeft</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>showDamageText</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>damageTextThrottleMs</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>shakeAmplitude</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>shakeDurationMs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -609,6 +629,26 @@
           <t>int</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -704,6 +744,26 @@
       <c r="S3" t="inlineStr">
         <is>
           <t>怪物美术的默认朝向是否朝左：1=朝左（★已实测确认：无翻转时怪物面朝左）。注意：朝向观感主要由 BaseEnemy.SetPath 的"初始朝向=路径第一段横向方向"决定，本值只影响翻转方向</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>是否显示伤害飘字 0否/1是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>同一怪物两次伤害飘字的最小间隔（毫秒），防止高频攻击刷屏</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>屏幕震动幅度（世界单位）；0=不震</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>屏幕震动持续时间（毫秒）</t>
         </is>
       </c>
     </row>
@@ -761,6 +821,18 @@
       </c>
       <c r="S4" t="n">
         <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/Global.xlsx
+++ b/Luban/Config/Datas/Global.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Luban/Config/Datas/Global.xlsx
+++ b/Luban/Config/Datas/Global.xlsx
@@ -811,7 +811,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>

--- a/Luban/Config/Datas/Global.xlsx
+++ b/Luban/Config/Datas/Global.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,107 +429,37 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>cellSize</t>
+          <t>enemyPoolSize</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>boardOriginPadding</t>
+          <t>bulletPoolSize</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>enemyPoolSize</t>
+          <t>maxEnemyAlive</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>bulletPoolSize</t>
+          <t>targetFrameRate</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>maxEnemyAlive</t>
+          <t>deathRecycleDelayMs</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>defaultReward</t>
+          <t>checkOfflinePerFrame</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>defaultDamageToPlayer</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>defaultBodyRadius</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>defaultSearchIntervalMs</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>targetFrameRate</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>deathRecycleDelayMs</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>checkOfflinePerFrame</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
           <t>showDebugLog</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>autoNextRoundDelayMs</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>autoStartRoundDelayMs</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>sellRefundRate</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>artFaceLeft</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>showDamageText</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>damageTextThrottleMs</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>shakeAmplitude</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>shakeDurationMs</t>
         </is>
       </c>
     </row>
@@ -546,12 +476,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -575,76 +505,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -663,107 +523,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>棋盘格子边长（世界单位）</t>
+          <t>怪物对象池初始容量</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>棋盘相对相机中心的留白（世界单位）</t>
+          <t>子弹对象池初始容量</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>怪物对象池初始容量</t>
+          <t>同屏怪物上限（性能保护）</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>子弹对象池初始容量</t>
+          <t>目标帧率</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>同屏怪物上限（性能保护）</t>
+          <t>死亡动画播完后延迟回收的时间</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>未配 reward 时的默认击杀奖励</t>
+          <t>每帧最多重算路径次数（防止卡顿）</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>未配 damageToPlayer 时的默认漏怪伤害</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>未配 bodyRadius 时的默认受击半径</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>未配 searchIntervalMs 时的默认索敌间隔</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>目标帧率</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>死亡动画播完后延迟回收的时间</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>每帧最多重算路径次数（防止卡顿）</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
           <t>是否打印战斗自检日志 0否/1是</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>回合完成后自动开始下一回合的延迟（毫秒）；0=不自动，需手动点「下一回合」</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>关卡就绪后自动开始第一回合的延迟（毫秒）；0=等玩家点「开始」（建议留 0，好让玩家先布防）</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>售卖返还比例（乘在 TBTowerInfo.sellPrice 上）；1.0=按配置的 sellPrice 全额返还</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>怪物美术的默认朝向是否朝左：1=朝左（★已实测确认：无翻转时怪物面朝左）。注意：朝向观感主要由 BaseEnemy.SetPath 的"初始朝向=路径第一段横向方向"决定，本值只影响翻转方向</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>是否显示伤害飘字 0否/1是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>同一怪物两次伤害飘字的最小间隔（毫秒），防止高频攻击刷屏</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>屏幕震动幅度（世界单位）；0=不震</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>屏幕震动持续时间（毫秒）</t>
         </is>
       </c>
     </row>
@@ -772,67 +562,25 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
+        <v>256</v>
+      </c>
+      <c r="D4" t="n">
+        <v>128</v>
+      </c>
+      <c r="E4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F4" t="n">
+        <v>60</v>
+      </c>
+      <c r="G4" t="n">
+        <v>600</v>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>256</v>
-      </c>
-      <c r="F4" t="n">
-        <v>128</v>
-      </c>
-      <c r="G4" t="n">
-        <v>200</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>100</v>
-      </c>
-      <c r="L4" t="n">
-        <v>60</v>
-      </c>
-      <c r="M4" t="n">
-        <v>600</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>120</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>180</v>
       </c>
     </row>
   </sheetData>
